--- a/output/pdf_financials_xlsx/CVGR.xlsx
+++ b/output/pdf_financials_xlsx/CVGR.xlsx
@@ -581,13 +581,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.381085</v>
+        <v>1.13984</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.946071</v>
+        <v>1.329061</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.378654</v>
+        <v>1.225966</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.372503</v>
+        <v>-1.131258</v>
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.378654</v>
+        <v>-1.225966</v>
       </c>
     </row>
     <row r="12">
@@ -615,7 +615,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.03564</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -885,7 +885,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.448592</v>
+        <v>-2.484232</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.38815</v>
@@ -917,7 +917,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.149272</v>
+        <v>-2.184912</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.38815</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-25043.95245863435</v>
+        <v>-25459.24027033326</v>
       </c>
       <c r="C30" s="1" t="inlineStr">
         <is>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000343</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.114539</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.009487000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1028,13 +1028,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000343</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.114539</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.009487000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1223,10 +1223,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.114539</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.009487000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -4800,7 +4800,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">

--- a/output/pdf_financials_xlsx/CVGR.xlsx
+++ b/output/pdf_financials_xlsx/CVGR.xlsx
@@ -1534,13 +1534,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.956843</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.814932</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.008639</v>
       </c>
     </row>
     <row r="68">
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.029751</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -3899,7 +3899,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.029751</v>
       </c>
